--- a/CYP2C9/CYP2C9_Allele_def_rs_excluidos.xlsx
+++ b/CYP2C9/CYP2C9_Allele_def_rs_excluidos.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="X:\Fobos\Proyecto_Diana\TFM_GenoStaR\CYP2C9\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23010" windowHeight="9015" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Salida_R" sheetId="1" r:id="rId1"/>
@@ -4145,7 +4145,6 @@
         <v>137</v>
       </c>
       <c r="AP43" s="5">
-        <f>SUM(AP4:AP42)*100</f>
         <v>3.58746E-2</v>
       </c>
     </row>

--- a/CYP2C9/CYP2C9_Allele_def_rs_excluidos.xlsx
+++ b/CYP2C9/CYP2C9_Allele_def_rs_excluidos.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23010" windowHeight="9015" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="25200" windowHeight="11160" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Salida_R" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="441" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="175">
   <si>
     <t>rsID</t>
   </si>
@@ -479,6 +479,72 @@
   </si>
   <si>
     <t>https://gnomad.broadinstitute.org/variant/10-94986174-G-C?dataset=gnomad_r4</t>
+  </si>
+  <si>
+    <t>Corresponde a rs1216169538 (CYP2C9_allele_definition_table)</t>
+  </si>
+  <si>
+    <t>https://gnomad.broadinstitute.org/variant/10-94941915-G-T?dataset=gnomad_r4</t>
+  </si>
+  <si>
+    <t>Corresponde a rs2493006942 (CYP2C9_allele_definition_table)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dbSNP </t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs2493006942</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs761033063</t>
+  </si>
+  <si>
+    <t>Corresponde a rs2492587526 (CYP2C9_allele_definition_table)</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs2492587526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corresponde a rs761033063 (CYP2C9_allele_definition_table) </t>
+  </si>
+  <si>
+    <t>Corresponde a rs2492591692 (CYP2C9_allele_definition_table)</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs2492591692</t>
+  </si>
+  <si>
+    <t>Corresponde a rs2492634549 (CYP2C9_allele_definition_table)</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs2492634549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Corresponde a rs2492650213 (CYP2C9_allele_definition_table) </t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs2492650213</t>
+  </si>
+  <si>
+    <t>Corresponde a rs2492662738 (CYP2C9_allele_definition_table)</t>
+  </si>
+  <si>
+    <t>dnSNP</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs2492662738</t>
+  </si>
+  <si>
+    <t>Corresponde a rs2492662839 (CYP2C9_allele_definition_table)</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs2492662839</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Corresponde a rs1311013151 (posicion UCSC)</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs1311013151</t>
   </si>
 </sst>
 </file>
@@ -510,7 +576,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -532,6 +598,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B0F0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -564,7 +636,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -583,6 +655,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="11" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -1684,17 +1765,17 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AR44"/>
+  <dimension ref="A1:AS44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="39" width="9.140625" style="3"/>
     <col min="40" max="40" width="14.28515625" style="3" customWidth="1"/>
-    <col min="41" max="41" width="20.5703125" style="3" customWidth="1"/>
-    <col min="42" max="42" width="13" style="3" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="3"/>
+    <col min="41" max="42" width="20.5703125" style="3" customWidth="1"/>
+    <col min="43" max="43" width="13" style="3" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:44" s="2" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:45" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1818,17 +1899,18 @@
       <c r="AO1" s="4" t="s">
         <v>133</v>
       </c>
-      <c r="AP1" s="4" t="s">
+      <c r="AP1" s="4"/>
+      <c r="AQ1" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="AQ1" s="4" t="s">
+      <c r="AR1" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="AR1" s="4" t="s">
+      <c r="AS1" s="4" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>40</v>
       </c>
@@ -1875,8 +1957,9 @@
       <c r="AP2" s="5"/>
       <c r="AQ2" s="5"/>
       <c r="AR2" s="5"/>
-    </row>
-    <row r="3" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS2" s="5"/>
+    </row>
+    <row r="3" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>41</v>
       </c>
@@ -2001,8 +2084,9 @@
       <c r="AP3" s="5"/>
       <c r="AQ3" s="5"/>
       <c r="AR3" s="5"/>
-    </row>
-    <row r="4" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS3" s="5"/>
+    </row>
+    <row r="4" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>52</v>
       </c>
@@ -2050,17 +2134,18 @@
       <c r="AO4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="AP4">
+      <c r="AP4" s="10"/>
+      <c r="AQ4">
         <v>3.3900000000000002E-6</v>
       </c>
-      <c r="AQ4" s="5" t="s">
+      <c r="AR4" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR4" s="5" t="s">
+      <c r="AS4" s="5" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>62</v>
       </c>
@@ -2108,11 +2193,20 @@
       <c r="AO5" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="AP5" s="5"/>
-      <c r="AQ5" s="5"/>
-      <c r="AR5" s="5"/>
-    </row>
-    <row r="6" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AP5" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="AQ5" s="14">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="AR5" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS5" s="5" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>67</v>
       </c>
@@ -2160,17 +2254,18 @@
       <c r="AO6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AP6">
+      <c r="AP6" s="10"/>
+      <c r="AQ6">
         <v>1.102E-5</v>
       </c>
-      <c r="AQ6" s="5" t="s">
+      <c r="AR6" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR6" s="5" t="s">
+      <c r="AS6" s="5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="7" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>68</v>
       </c>
@@ -2218,11 +2313,20 @@
       <c r="AO7" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="AP7" s="5"/>
-      <c r="AQ7" s="5"/>
-      <c r="AR7" s="5"/>
-    </row>
-    <row r="8" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AP7" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="AQ7" s="13">
+        <v>8.4750000000000004E-7</v>
+      </c>
+      <c r="AR7" s="5" t="s">
+        <v>138</v>
+      </c>
+      <c r="AS7" s="5" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="8" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>70</v>
       </c>
@@ -2270,17 +2374,18 @@
       <c r="AO8" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="AP8" s="5">
+      <c r="AP8" s="4"/>
+      <c r="AQ8" s="5">
         <v>0</v>
       </c>
-      <c r="AQ8" s="5" t="s">
+      <c r="AR8" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR8" s="5" t="s">
+      <c r="AS8" s="5" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="9" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>74</v>
       </c>
@@ -2328,17 +2433,18 @@
       <c r="AO9" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="AP9" s="5">
+      <c r="AP9" s="4"/>
+      <c r="AQ9" s="5">
         <v>0</v>
       </c>
-      <c r="AQ9" s="5" t="s">
+      <c r="AR9" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR9" s="8" t="s">
+      <c r="AS9" s="8" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>79</v>
       </c>
@@ -2386,17 +2492,18 @@
       <c r="AO10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AP10">
+      <c r="AP10" s="10"/>
+      <c r="AQ10">
         <v>7.9670000000000001E-5</v>
       </c>
-      <c r="AQ10" s="5" t="s">
+      <c r="AR10" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR10" s="5" t="s">
+      <c r="AS10" s="5" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="11" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>84</v>
       </c>
@@ -2444,11 +2551,20 @@
       <c r="AO11" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="AP11" s="5"/>
-      <c r="AQ11" s="5"/>
-      <c r="AR11" s="5"/>
-    </row>
-    <row r="12" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AP11" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="AQ11" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR11" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS11" s="5" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="12" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>86</v>
       </c>
@@ -2496,11 +2612,12 @@
       <c r="AO12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="AP12" s="5"/>
+      <c r="AP12" s="4"/>
       <c r="AQ12" s="5"/>
       <c r="AR12" s="5"/>
-    </row>
-    <row r="13" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS12" s="5"/>
+    </row>
+    <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>95</v>
       </c>
@@ -2548,11 +2665,12 @@
       <c r="AO13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="AP13" s="5"/>
+      <c r="AP13" s="4"/>
       <c r="AQ13" s="5"/>
       <c r="AR13" s="5"/>
-    </row>
-    <row r="14" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS13" s="5"/>
+    </row>
+    <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>96</v>
       </c>
@@ -2600,11 +2718,20 @@
       <c r="AO14" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="AP14" s="5"/>
-      <c r="AQ14" s="5"/>
-      <c r="AR14" s="5"/>
-    </row>
-    <row r="15" spans="1:44" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AP14" s="11" t="s">
+        <v>162</v>
+      </c>
+      <c r="AQ14" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS14" s="5" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="15" spans="1:45" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>97</v>
       </c>
@@ -2652,11 +2779,20 @@
       <c r="AO15" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AP15" s="5"/>
-      <c r="AQ15" s="5"/>
-      <c r="AR15" s="5"/>
-    </row>
-    <row r="16" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AP15" s="11" t="s">
+        <v>164</v>
+      </c>
+      <c r="AQ15" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR15" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS15" s="5" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="16" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>103</v>
       </c>
@@ -2704,11 +2840,12 @@
       <c r="AO16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AP16" s="5"/>
+      <c r="AP16" s="4"/>
       <c r="AQ16" s="5"/>
       <c r="AR16" s="5"/>
-    </row>
-    <row r="17" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS16" s="5"/>
+    </row>
+    <row r="17" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>105</v>
       </c>
@@ -2756,11 +2893,20 @@
       <c r="AO17" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="AP17" s="5"/>
-      <c r="AQ17" s="5"/>
-      <c r="AR17" s="5"/>
-    </row>
-    <row r="18" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AP17" s="11" t="s">
+        <v>168</v>
+      </c>
+      <c r="AQ17" s="14">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="AR17" s="5" t="s">
+        <v>169</v>
+      </c>
+      <c r="AS17" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="18" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>106</v>
       </c>
@@ -2808,15 +2954,16 @@
       <c r="AO18" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="AP18" s="5">
+      <c r="AP18" s="5"/>
+      <c r="AQ18" s="5">
         <v>0</v>
       </c>
-      <c r="AQ18" s="5" t="s">
+      <c r="AR18" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="AR18" s="5"/>
-    </row>
-    <row r="19" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS18" s="5"/>
+    </row>
+    <row r="19" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>107</v>
       </c>
@@ -2864,17 +3011,18 @@
       <c r="AO19" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="AP19" s="5">
+      <c r="AP19" s="4"/>
+      <c r="AQ19" s="5">
         <v>0</v>
       </c>
-      <c r="AQ19" s="5" t="s">
+      <c r="AR19" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR19" s="5" t="s">
+      <c r="AS19" s="5" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="20" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>108</v>
       </c>
@@ -2922,15 +3070,16 @@
       <c r="AO20" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="AP20" s="5">
+      <c r="AP20" s="5"/>
+      <c r="AQ20" s="5">
         <v>1E-4</v>
       </c>
-      <c r="AQ20" s="5" t="s">
+      <c r="AR20" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="AR20" s="5"/>
-    </row>
-    <row r="21" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS20" s="5"/>
+    </row>
+    <row r="21" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>109</v>
       </c>
@@ -2978,15 +3127,16 @@
       <c r="AO21" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="AP21" s="5">
+      <c r="AP21" s="5"/>
+      <c r="AQ21" s="5">
         <v>0</v>
       </c>
-      <c r="AQ21" s="5" t="s">
+      <c r="AR21" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="AR21" s="5"/>
-    </row>
-    <row r="22" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS21" s="5"/>
+    </row>
+    <row r="22" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>110</v>
       </c>
@@ -3034,11 +3184,12 @@
       <c r="AO22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AP22" s="5"/>
+      <c r="AP22" s="4"/>
       <c r="AQ22" s="5"/>
       <c r="AR22" s="5"/>
-    </row>
-    <row r="23" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS22" s="5"/>
+    </row>
+    <row r="23" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>111</v>
       </c>
@@ -3086,11 +3237,12 @@
       <c r="AO23" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AP23" s="5"/>
+      <c r="AP23" s="4"/>
       <c r="AQ23" s="5"/>
       <c r="AR23" s="5"/>
-    </row>
-    <row r="24" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS23" s="5"/>
+    </row>
+    <row r="24" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>112</v>
       </c>
@@ -3138,15 +3290,16 @@
       <c r="AO24" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="AP24" s="5">
+      <c r="AP24" s="5"/>
+      <c r="AQ24" s="5">
         <v>0</v>
       </c>
-      <c r="AQ24" s="5" t="s">
+      <c r="AR24" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="AR24" s="5"/>
-    </row>
-    <row r="25" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS24" s="5"/>
+    </row>
+    <row r="25" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>113</v>
       </c>
@@ -3194,15 +3347,16 @@
       <c r="AO25" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="AP25" s="5">
+      <c r="AP25" s="5"/>
+      <c r="AQ25" s="5">
         <v>0</v>
       </c>
-      <c r="AQ25" s="5" t="s">
+      <c r="AR25" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="AR25" s="5"/>
-    </row>
-    <row r="26" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS25" s="5"/>
+    </row>
+    <row r="26" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>114</v>
       </c>
@@ -3250,17 +3404,18 @@
       <c r="AO26" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AP26">
+      <c r="AP26" s="10"/>
+      <c r="AQ26">
         <v>7.6290000000000001E-6</v>
       </c>
-      <c r="AQ26" s="5" t="s">
+      <c r="AR26" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR26" s="5" t="s">
+      <c r="AS26" s="5" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>115</v>
       </c>
@@ -3308,11 +3463,20 @@
       <c r="AO27" s="7" t="s">
         <v>17</v>
       </c>
-      <c r="AP27" s="5"/>
-      <c r="AQ27" s="5"/>
-      <c r="AR27" s="5"/>
-    </row>
-    <row r="28" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AP27" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="AQ27" s="12">
+        <v>0</v>
+      </c>
+      <c r="AR27" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS27" s="5" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="28" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>116</v>
       </c>
@@ -3360,11 +3524,20 @@
       <c r="AO28" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="AP28" s="5"/>
-      <c r="AQ28" s="5"/>
-      <c r="AR28" s="5"/>
-    </row>
-    <row r="29" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AP28" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="AQ28" s="14">
+        <v>8.9999999999999996E-7</v>
+      </c>
+      <c r="AR28" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS28" s="5" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>118</v>
       </c>
@@ -3412,15 +3585,16 @@
       <c r="AO29" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="AP29" s="5">
+      <c r="AP29" s="5"/>
+      <c r="AQ29" s="5">
         <v>0</v>
       </c>
-      <c r="AQ29" s="5" t="s">
+      <c r="AR29" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="AR29" s="5"/>
-    </row>
-    <row r="30" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS29" s="5"/>
+    </row>
+    <row r="30" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>119</v>
       </c>
@@ -3468,15 +3642,16 @@
       <c r="AO30" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="AP30" s="5">
+      <c r="AP30" s="5"/>
+      <c r="AQ30" s="5">
         <v>1E-4</v>
       </c>
-      <c r="AQ30" s="5" t="s">
+      <c r="AR30" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="AR30" s="5"/>
-    </row>
-    <row r="31" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS30" s="5"/>
+    </row>
+    <row r="31" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>120</v>
       </c>
@@ -3524,17 +3699,18 @@
       <c r="AO31" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AP31">
+      <c r="AP31" s="10"/>
+      <c r="AQ31">
         <v>4.2390000000000004E-6</v>
       </c>
-      <c r="AQ31" s="5" t="s">
+      <c r="AR31" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR31" s="5" t="s">
+      <c r="AS31" s="5" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="32" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>121</v>
       </c>
@@ -3582,15 +3758,16 @@
       <c r="AO32" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="AP32" s="5">
+      <c r="AP32" s="5"/>
+      <c r="AQ32" s="5">
         <v>0</v>
       </c>
-      <c r="AQ32" s="5" t="s">
+      <c r="AR32" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="AR32" s="5"/>
-    </row>
-    <row r="33" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS32" s="5"/>
+    </row>
+    <row r="33" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>122</v>
       </c>
@@ -3638,17 +3815,18 @@
       <c r="AO33" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="AP33">
+      <c r="AP33" s="10"/>
+      <c r="AQ33">
         <v>1.102E-5</v>
       </c>
-      <c r="AQ33" s="5" t="s">
+      <c r="AR33" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR33" s="5" t="s">
+      <c r="AS33" s="5" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>123</v>
       </c>
@@ -3696,11 +3874,20 @@
       <c r="AO34" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="AP34" s="5"/>
-      <c r="AQ34" s="5"/>
-      <c r="AR34" s="5"/>
-    </row>
-    <row r="35" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AP34" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="AQ34" s="14">
+        <v>1.9999999999999999E-6</v>
+      </c>
+      <c r="AR34" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS34" s="5" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="35" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>124</v>
       </c>
@@ -3748,17 +3935,18 @@
       <c r="AO35" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="AP35" s="5">
+      <c r="AP35" s="4"/>
+      <c r="AQ35" s="5">
         <v>0</v>
       </c>
-      <c r="AQ35" s="5" t="s">
+      <c r="AR35" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR35" s="5" t="s">
+      <c r="AS35" s="5" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>125</v>
       </c>
@@ -3806,17 +3994,18 @@
       <c r="AO36" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="AP36" s="5">
+      <c r="AP36" s="4"/>
+      <c r="AQ36" s="5">
         <v>0</v>
       </c>
-      <c r="AQ36" s="5" t="s">
+      <c r="AR36" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR36" s="5" t="s">
+      <c r="AS36" s="5" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="37" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>126</v>
       </c>
@@ -3864,11 +4053,12 @@
       <c r="AO37" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AP37" s="5"/>
+      <c r="AP37" s="4"/>
       <c r="AQ37" s="5"/>
       <c r="AR37" s="5"/>
-    </row>
-    <row r="38" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS37" s="5"/>
+    </row>
+    <row r="38" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>127</v>
       </c>
@@ -3916,11 +4106,12 @@
       <c r="AO38" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AP38" s="5"/>
+      <c r="AP38" s="4"/>
       <c r="AQ38" s="5"/>
       <c r="AR38" s="5"/>
-    </row>
-    <row r="39" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS38" s="5"/>
+    </row>
+    <row r="39" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>128</v>
       </c>
@@ -3968,17 +4159,18 @@
       <c r="AO39" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AP39">
+      <c r="AP39" s="10"/>
+      <c r="AQ39">
         <v>4.0930000000000003E-5</v>
       </c>
-      <c r="AQ39" s="5" t="s">
+      <c r="AR39" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR39" s="5" t="s">
+      <c r="AS39" s="5" t="s">
         <v>151</v>
       </c>
     </row>
-    <row r="40" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>129</v>
       </c>
@@ -4026,11 +4218,20 @@
       <c r="AO40" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="AP40" s="5"/>
-      <c r="AQ40" s="5"/>
-      <c r="AR40" s="5"/>
-    </row>
-    <row r="41" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AP40" s="11" t="s">
+        <v>173</v>
+      </c>
+      <c r="AQ40" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR40" s="5" t="s">
+        <v>156</v>
+      </c>
+      <c r="AS40" s="5" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="41" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>130</v>
       </c>
@@ -4078,17 +4279,18 @@
       <c r="AO41" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AP41" s="9">
+      <c r="AP41" s="10"/>
+      <c r="AQ41" s="9">
         <v>8.4799999999999997E-7</v>
       </c>
-      <c r="AQ41" s="5" t="s">
+      <c r="AR41" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AR41" s="5" t="s">
+      <c r="AS41" s="5" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="42" spans="1:44" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>131</v>
       </c>
@@ -4136,24 +4338,25 @@
       <c r="AO42" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AP42" s="5"/>
+      <c r="AP42" s="4"/>
       <c r="AQ42" s="5"/>
       <c r="AR42" s="5"/>
-    </row>
-    <row r="43" spans="1:44" x14ac:dyDescent="0.25">
+      <c r="AS42" s="5"/>
+    </row>
+    <row r="43" spans="1:45" x14ac:dyDescent="0.25">
       <c r="AO43" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="AP43" s="5">
-        <v>3.58746E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="1:44" x14ac:dyDescent="0.25">
-      <c r="AP44" s="5"/>
+      <c r="AQ43" s="5">
+        <v>3.6649350000000004E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:45" x14ac:dyDescent="0.25">
+      <c r="AQ44" s="5"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="AR9" r:id="rId1"/>
+    <hyperlink ref="AS9" r:id="rId1"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/CYP2C9/CYP2C9_Allele_def_rs_excluidos.xlsx
+++ b/CYP2C9/CYP2C9_Allele_def_rs_excluidos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="471" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="184">
   <si>
     <t>rsID</t>
   </si>
@@ -545,6 +545,33 @@
   </si>
   <si>
     <t>https://www.ncbi.nlm.nih.gov/snp/rs1311013151</t>
+  </si>
+  <si>
+    <t>https://www.clinpgx.org/haplotype/PA166048686</t>
+  </si>
+  <si>
+    <t>https://www.clinpgx.org/haplotype/PA166048695</t>
+  </si>
+  <si>
+    <t>https://www.clinpgx.org/haplotype/PA166048703</t>
+  </si>
+  <si>
+    <t>https://www.clinpgx.org/haplotype/PA166243718</t>
+  </si>
+  <si>
+    <t>https://www.clinpgx.org/haplotype/PA166243719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ClinPGX </t>
+  </si>
+  <si>
+    <t>https://www.clinpgx.org/haplotype/PA166269375</t>
+  </si>
+  <si>
+    <t>https://www.clinpgx.org/haplotype/PA166269376</t>
+  </si>
+  <si>
+    <t>https://www.clinpgx.org/haplotype/PA166269380</t>
   </si>
 </sst>
 </file>
@@ -636,7 +663,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -664,6 +691,9 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
@@ -2612,10 +2642,18 @@
       <c r="AO12" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="AP12" s="4"/>
-      <c r="AQ12" s="5"/>
-      <c r="AR12" s="5"/>
-      <c r="AS12" s="5"/>
+      <c r="AP12" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="AQ12" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AS12" s="5" t="s">
+        <v>175</v>
+      </c>
     </row>
     <row r="13" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
@@ -2665,10 +2703,18 @@
       <c r="AO13" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="AP13" s="4"/>
-      <c r="AQ13" s="5"/>
-      <c r="AR13" s="5"/>
-      <c r="AS13" s="5"/>
+      <c r="AP13" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="AQ13" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR13" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AS13" s="5" t="s">
+        <v>176</v>
+      </c>
     </row>
     <row r="14" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
@@ -2840,10 +2886,18 @@
       <c r="AO16" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="AP16" s="4"/>
-      <c r="AQ16" s="5"/>
-      <c r="AR16" s="5"/>
-      <c r="AS16" s="5"/>
+      <c r="AP16" s="15" t="s">
+        <v>103</v>
+      </c>
+      <c r="AQ16" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AS16" s="5" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="17" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
@@ -3184,10 +3238,18 @@
       <c r="AO22" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="AP22" s="4"/>
-      <c r="AQ22" s="5"/>
-      <c r="AR22" s="5"/>
-      <c r="AS22" s="5"/>
+      <c r="AP22" s="15" t="s">
+        <v>110</v>
+      </c>
+      <c r="AQ22" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR22" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AS22" s="5" t="s">
+        <v>178</v>
+      </c>
     </row>
     <row r="23" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
@@ -3237,10 +3299,18 @@
       <c r="AO23" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="AP23" s="4"/>
-      <c r="AQ23" s="5"/>
-      <c r="AR23" s="5"/>
-      <c r="AS23" s="5"/>
+      <c r="AP23" s="15" t="s">
+        <v>111</v>
+      </c>
+      <c r="AQ23" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR23" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="AS23" s="5" t="s">
+        <v>179</v>
+      </c>
     </row>
     <row r="24" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
@@ -4053,10 +4123,18 @@
       <c r="AO37" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="AP37" s="4"/>
-      <c r="AQ37" s="5"/>
-      <c r="AR37" s="5"/>
-      <c r="AS37" s="5"/>
+      <c r="AP37" s="15" t="s">
+        <v>126</v>
+      </c>
+      <c r="AQ37" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR37" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AS37" s="5" t="s">
+        <v>181</v>
+      </c>
     </row>
     <row r="38" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
@@ -4106,10 +4184,18 @@
       <c r="AO38" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="AP38" s="4"/>
-      <c r="AQ38" s="5"/>
-      <c r="AR38" s="5"/>
-      <c r="AS38" s="5"/>
+      <c r="AP38" s="15" t="s">
+        <v>127</v>
+      </c>
+      <c r="AQ38" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR38" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AS38" s="5" t="s">
+        <v>182</v>
+      </c>
     </row>
     <row r="39" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
@@ -4338,10 +4424,18 @@
       <c r="AO42" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="AP42" s="4"/>
-      <c r="AQ42" s="5"/>
-      <c r="AR42" s="5"/>
-      <c r="AS42" s="5"/>
+      <c r="AP42" s="15" t="s">
+        <v>131</v>
+      </c>
+      <c r="AQ42" s="5">
+        <v>0</v>
+      </c>
+      <c r="AR42" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="AS42" s="5" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="43" spans="1:45" x14ac:dyDescent="0.25">
       <c r="AO43" s="3" t="s">

--- a/CYP2C9/CYP2C9_Allele_def_rs_excluidos.xlsx
+++ b/CYP2C9/CYP2C9_Allele_def_rs_excluidos.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="503" uniqueCount="193">
   <si>
     <t>rsID</t>
   </si>
@@ -572,6 +572,33 @@
   </si>
   <si>
     <t>https://www.clinpgx.org/haplotype/PA166269380</t>
+  </si>
+  <si>
+    <t>https://www.ncbi.nlm.nih.gov/snp/rs767284820</t>
+  </si>
+  <si>
+    <t>dbSNP</t>
+  </si>
+  <si>
+    <t>https://gnomad.broadinstitute.org/variant/10-94942233-C-T?dataset=gnomad_r4</t>
+  </si>
+  <si>
+    <t>https://gnomad.broadinstitute.org/variant/10-94942291-G-A?dataset=gnomad_r4</t>
+  </si>
+  <si>
+    <t>https://gnomad.broadinstitute.org/variant/10-94981305-C-G?dataset=gnomad_r4</t>
+  </si>
+  <si>
+    <t>https://gnomad.broadinstitute.org/variant/10-94988852-C-T?dataset=gnomad_r4</t>
+  </si>
+  <si>
+    <t>https://gnomad.broadinstitute.org/variant/10-94942306-C-T?dataset=gnomad_r4</t>
+  </si>
+  <si>
+    <t>https://gnomad.broadinstitute.org/variant/10-94942308-C-T?dataset=gnomad_r4</t>
+  </si>
+  <si>
+    <t>https://gnomad.broadinstitute.org/variant/10-94986136-A-C?dataset=gnomad_r4</t>
   </si>
 </sst>
 </file>
@@ -663,7 +690,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -676,7 +703,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2164,7 +2190,7 @@
       <c r="AO4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="AP4" s="10"/>
+      <c r="AP4" s="9"/>
       <c r="AQ4">
         <v>3.3900000000000002E-6</v>
       </c>
@@ -2220,13 +2246,13 @@
       <c r="AL5" s="5"/>
       <c r="AM5" s="5"/>
       <c r="AN5" s="5"/>
-      <c r="AO5" s="7" t="s">
+      <c r="AO5" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="AP5" s="11" t="s">
+      <c r="AP5" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="AQ5" s="14">
+      <c r="AQ5" s="13">
         <v>1.9999999999999999E-6</v>
       </c>
       <c r="AR5" s="5" t="s">
@@ -2284,7 +2310,7 @@
       <c r="AO6" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="AP6" s="10"/>
+      <c r="AP6" s="9"/>
       <c r="AQ6">
         <v>1.102E-5</v>
       </c>
@@ -2340,13 +2366,13 @@
       <c r="AL7" s="5"/>
       <c r="AM7" s="5"/>
       <c r="AN7" s="5"/>
-      <c r="AO7" s="7" t="s">
+      <c r="AO7" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="AP7" s="11" t="s">
+      <c r="AP7" s="10" t="s">
         <v>153</v>
       </c>
-      <c r="AQ7" s="13">
+      <c r="AQ7" s="12">
         <v>8.4750000000000004E-7</v>
       </c>
       <c r="AR7" s="5" t="s">
@@ -2470,7 +2496,7 @@
       <c r="AR9" s="5" t="s">
         <v>138</v>
       </c>
-      <c r="AS9" s="8" t="s">
+      <c r="AS9" s="7" t="s">
         <v>142</v>
       </c>
     </row>
@@ -2522,7 +2548,7 @@
       <c r="AO10" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="AP10" s="10"/>
+      <c r="AP10" s="9"/>
       <c r="AQ10">
         <v>7.9670000000000001E-5</v>
       </c>
@@ -2578,13 +2604,13 @@
       <c r="AL11" s="5"/>
       <c r="AM11" s="5"/>
       <c r="AN11" s="5"/>
-      <c r="AO11" s="7" t="s">
+      <c r="AO11" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="AP11" s="11" t="s">
+      <c r="AP11" s="10" t="s">
         <v>161</v>
       </c>
-      <c r="AQ11" s="12">
+      <c r="AQ11" s="11">
         <v>0</v>
       </c>
       <c r="AR11" s="5" t="s">
@@ -2639,10 +2665,10 @@
       <c r="AL12" s="5"/>
       <c r="AM12" s="5"/>
       <c r="AN12" s="5"/>
-      <c r="AO12" s="7" t="s">
+      <c r="AO12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="AP12" s="15" t="s">
+      <c r="AP12" s="14" t="s">
         <v>86</v>
       </c>
       <c r="AQ12" s="5">
@@ -2700,10 +2726,10 @@
       <c r="AL13" s="5"/>
       <c r="AM13" s="5"/>
       <c r="AN13" s="5"/>
-      <c r="AO13" s="7" t="s">
+      <c r="AO13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="AP13" s="15" t="s">
+      <c r="AP13" s="14" t="s">
         <v>95</v>
       </c>
       <c r="AQ13" s="5">
@@ -2761,13 +2787,13 @@
       <c r="AL14" s="5"/>
       <c r="AM14" s="5"/>
       <c r="AN14" s="5"/>
-      <c r="AO14" s="7" t="s">
+      <c r="AO14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="AP14" s="11" t="s">
+      <c r="AP14" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="AQ14" s="12">
+      <c r="AQ14" s="11">
         <v>0</v>
       </c>
       <c r="AR14" s="5" t="s">
@@ -2822,13 +2848,13 @@
       <c r="AL15" s="5"/>
       <c r="AM15" s="5"/>
       <c r="AN15" s="5"/>
-      <c r="AO15" s="7" t="s">
+      <c r="AO15" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="AP15" s="11" t="s">
+      <c r="AP15" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="AQ15" s="12">
+      <c r="AQ15" s="11">
         <v>0</v>
       </c>
       <c r="AR15" s="5" t="s">
@@ -2883,10 +2909,10 @@
       <c r="AL16" s="5"/>
       <c r="AM16" s="5"/>
       <c r="AN16" s="5"/>
-      <c r="AO16" s="7" t="s">
+      <c r="AO16" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="AP16" s="15" t="s">
+      <c r="AP16" s="14" t="s">
         <v>103</v>
       </c>
       <c r="AQ16" s="5">
@@ -2944,13 +2970,13 @@
       <c r="AL17" s="5"/>
       <c r="AM17" s="5"/>
       <c r="AN17" s="5"/>
-      <c r="AO17" s="7" t="s">
+      <c r="AO17" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="AP17" s="11" t="s">
+      <c r="AP17" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="AQ17" s="14">
+      <c r="AQ17" s="13">
         <v>1.9999999999999999E-6</v>
       </c>
       <c r="AR17" s="5" t="s">
@@ -3005,17 +3031,19 @@
       <c r="AN18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="AO18" s="6" t="s">
-        <v>106</v>
+      <c r="AO18" s="4" t="s">
+        <v>39</v>
       </c>
       <c r="AP18" s="5"/>
       <c r="AQ18" s="5">
         <v>0</v>
       </c>
       <c r="AR18" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="AS18" s="5"/>
+        <v>185</v>
+      </c>
+      <c r="AS18" s="5" t="s">
+        <v>184</v>
+      </c>
     </row>
     <row r="19" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
@@ -3121,17 +3149,19 @@
       <c r="AL20" s="5"/>
       <c r="AM20" s="5"/>
       <c r="AN20" s="5"/>
-      <c r="AO20" s="6" t="s">
-        <v>108</v>
+      <c r="AO20" s="4" t="s">
+        <v>11</v>
       </c>
       <c r="AP20" s="5"/>
-      <c r="AQ20" s="5">
-        <v>1E-4</v>
+      <c r="AQ20">
+        <v>1.059E-4</v>
       </c>
       <c r="AR20" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="AS20" s="5"/>
+        <v>138</v>
+      </c>
+      <c r="AS20" s="5" t="s">
+        <v>186</v>
+      </c>
     </row>
     <row r="21" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
@@ -3178,17 +3208,19 @@
       <c r="AL21" s="5"/>
       <c r="AM21" s="5"/>
       <c r="AN21" s="5"/>
-      <c r="AO21" s="6" t="s">
-        <v>109</v>
+      <c r="AO21" s="4" t="s">
+        <v>14</v>
       </c>
       <c r="AP21" s="5"/>
-      <c r="AQ21" s="5">
-        <v>0</v>
+      <c r="AQ21">
+        <v>1.102E-5</v>
       </c>
       <c r="AR21" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="AS21" s="5"/>
+        <v>138</v>
+      </c>
+      <c r="AS21" s="5" t="s">
+        <v>187</v>
+      </c>
     </row>
     <row r="22" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
@@ -3235,10 +3267,10 @@
       <c r="AL22" s="5"/>
       <c r="AM22" s="5"/>
       <c r="AN22" s="5"/>
-      <c r="AO22" s="7" t="s">
+      <c r="AO22" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="AP22" s="15" t="s">
+      <c r="AP22" s="14" t="s">
         <v>110</v>
       </c>
       <c r="AQ22" s="5">
@@ -3296,10 +3328,10 @@
       <c r="AL23" s="5"/>
       <c r="AM23" s="5"/>
       <c r="AN23" s="5"/>
-      <c r="AO23" s="7" t="s">
+      <c r="AO23" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="AP23" s="15" t="s">
+      <c r="AP23" s="14" t="s">
         <v>111</v>
       </c>
       <c r="AQ23" s="5">
@@ -3357,17 +3389,19 @@
       <c r="AL24" s="5"/>
       <c r="AM24" s="5"/>
       <c r="AN24" s="5"/>
-      <c r="AO24" s="6" t="s">
-        <v>112</v>
+      <c r="AO24" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="AP24" s="5"/>
-      <c r="AQ24" s="5">
-        <v>0</v>
+      <c r="AQ24" s="8">
+        <v>8.4750000000000004E-7</v>
       </c>
       <c r="AR24" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="AS24" s="5"/>
+        <v>138</v>
+      </c>
+      <c r="AS24" s="5" t="s">
+        <v>188</v>
+      </c>
     </row>
     <row r="25" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
@@ -3414,17 +3448,19 @@
       <c r="AL25" s="5"/>
       <c r="AM25" s="5"/>
       <c r="AN25" s="5"/>
-      <c r="AO25" s="6" t="s">
-        <v>113</v>
+      <c r="AO25" s="4" t="s">
+        <v>35</v>
       </c>
       <c r="AP25" s="5"/>
-      <c r="AQ25" s="5">
-        <v>0</v>
+      <c r="AQ25">
+        <v>8.4759999999999998E-6</v>
       </c>
       <c r="AR25" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="AS25" s="5"/>
+        <v>138</v>
+      </c>
+      <c r="AS25" s="5" t="s">
+        <v>189</v>
+      </c>
     </row>
     <row r="26" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
@@ -3474,7 +3510,7 @@
       <c r="AO26" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="AP26" s="10"/>
+      <c r="AP26" s="9"/>
       <c r="AQ26">
         <v>7.6290000000000001E-6</v>
       </c>
@@ -3530,13 +3566,13 @@
       <c r="AL27" s="5"/>
       <c r="AM27" s="5"/>
       <c r="AN27" s="5"/>
-      <c r="AO27" s="7" t="s">
+      <c r="AO27" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="AP27" s="11" t="s">
+      <c r="AP27" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="AQ27" s="12">
+      <c r="AQ27" s="11">
         <v>0</v>
       </c>
       <c r="AR27" s="5" t="s">
@@ -3591,13 +3627,13 @@
       </c>
       <c r="AM28" s="5"/>
       <c r="AN28" s="5"/>
-      <c r="AO28" s="7" t="s">
+      <c r="AO28" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="AP28" s="11" t="s">
+      <c r="AP28" s="10" t="s">
         <v>171</v>
       </c>
-      <c r="AQ28" s="14">
+      <c r="AQ28" s="13">
         <v>8.9999999999999996E-7</v>
       </c>
       <c r="AR28" s="5" t="s">
@@ -3652,17 +3688,19 @@
       <c r="AL29" s="5"/>
       <c r="AM29" s="5"/>
       <c r="AN29" s="5"/>
-      <c r="AO29" s="6" t="s">
-        <v>118</v>
+      <c r="AO29" s="4" t="s">
+        <v>15</v>
       </c>
       <c r="AP29" s="5"/>
-      <c r="AQ29" s="5">
-        <v>0</v>
+      <c r="AQ29">
+        <v>4.2379999999999999E-6</v>
       </c>
       <c r="AR29" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="AS29" s="5"/>
+        <v>138</v>
+      </c>
+      <c r="AS29" s="5" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="30" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
@@ -3709,17 +3747,19 @@
       <c r="AL30" s="5"/>
       <c r="AM30" s="5"/>
       <c r="AN30" s="5"/>
-      <c r="AO30" s="6" t="s">
-        <v>119</v>
+      <c r="AO30" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="AP30" s="5"/>
-      <c r="AQ30" s="5">
-        <v>1E-4</v>
+      <c r="AQ30">
+        <v>4.1529999999999997E-5</v>
       </c>
       <c r="AR30" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="AS30" s="5"/>
+        <v>138</v>
+      </c>
+      <c r="AS30" s="5" t="s">
+        <v>191</v>
+      </c>
     </row>
     <row r="31" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
@@ -3769,7 +3809,7 @@
       <c r="AO31" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="AP31" s="10"/>
+      <c r="AP31" s="9"/>
       <c r="AQ31">
         <v>4.2390000000000004E-6</v>
       </c>
@@ -3825,17 +3865,19 @@
       <c r="AL32" s="5"/>
       <c r="AM32" s="5"/>
       <c r="AN32" s="5"/>
-      <c r="AO32" s="6" t="s">
-        <v>121</v>
+      <c r="AO32" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="AP32" s="5"/>
-      <c r="AQ32" s="5">
-        <v>0</v>
+      <c r="AQ32">
+        <v>1.102E-5</v>
       </c>
       <c r="AR32" s="5" t="s">
-        <v>145</v>
-      </c>
-      <c r="AS32" s="5"/>
+        <v>138</v>
+      </c>
+      <c r="AS32" s="5" t="s">
+        <v>192</v>
+      </c>
     </row>
     <row r="33" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
@@ -3885,7 +3927,7 @@
       <c r="AO33" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="AP33" s="10"/>
+      <c r="AP33" s="9"/>
       <c r="AQ33">
         <v>1.102E-5</v>
       </c>
@@ -3941,13 +3983,13 @@
       <c r="AL34" s="5"/>
       <c r="AM34" s="5"/>
       <c r="AN34" s="5"/>
-      <c r="AO34" s="7" t="s">
+      <c r="AO34" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="AP34" s="11" t="s">
+      <c r="AP34" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="AQ34" s="14">
+      <c r="AQ34" s="13">
         <v>1.9999999999999999E-6</v>
       </c>
       <c r="AR34" s="5" t="s">
@@ -4120,10 +4162,10 @@
       <c r="AL37" s="5"/>
       <c r="AM37" s="5"/>
       <c r="AN37" s="5"/>
-      <c r="AO37" s="7" t="s">
+      <c r="AO37" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="AP37" s="15" t="s">
+      <c r="AP37" s="14" t="s">
         <v>126</v>
       </c>
       <c r="AQ37" s="5">
@@ -4181,10 +4223,10 @@
       <c r="AL38" s="5"/>
       <c r="AM38" s="5"/>
       <c r="AN38" s="5"/>
-      <c r="AO38" s="7" t="s">
+      <c r="AO38" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="AP38" s="15" t="s">
+      <c r="AP38" s="14" t="s">
         <v>127</v>
       </c>
       <c r="AQ38" s="5">
@@ -4245,7 +4287,7 @@
       <c r="AO39" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="AP39" s="10"/>
+      <c r="AP39" s="9"/>
       <c r="AQ39">
         <v>4.0930000000000003E-5</v>
       </c>
@@ -4301,10 +4343,10 @@
       <c r="AL40" s="5"/>
       <c r="AM40" s="5"/>
       <c r="AN40" s="5"/>
-      <c r="AO40" s="7" t="s">
+      <c r="AO40" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="AP40" s="11" t="s">
+      <c r="AP40" s="10" t="s">
         <v>173</v>
       </c>
       <c r="AQ40" s="5">
@@ -4365,8 +4407,8 @@
       <c r="AO41" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="AP41" s="10"/>
-      <c r="AQ41" s="9">
+      <c r="AP41" s="9"/>
+      <c r="AQ41" s="8">
         <v>8.4799999999999997E-7</v>
       </c>
       <c r="AR41" s="5" t="s">
@@ -4421,10 +4463,10 @@
       <c r="AL42" s="5"/>
       <c r="AM42" s="5"/>
       <c r="AN42" s="5"/>
-      <c r="AO42" s="7" t="s">
+      <c r="AO42" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="AP42" s="15" t="s">
+      <c r="AP42" s="14" t="s">
         <v>131</v>
       </c>
       <c r="AQ42" s="5">
@@ -4442,7 +4484,8 @@
         <v>137</v>
       </c>
       <c r="AQ43" s="5">
-        <v>3.6649350000000004E-2</v>
+        <f>(SUM(AQ4:AQ42))*100</f>
+        <v>3.4952499999999997E-2</v>
       </c>
     </row>
     <row r="44" spans="1:45" x14ac:dyDescent="0.25">

--- a/CYP2C9/CYP2C9_Allele_def_rs_excluidos.xlsx
+++ b/CYP2C9/CYP2C9_Allele_def_rs_excluidos.xlsx
@@ -4484,7 +4484,6 @@
         <v>137</v>
       </c>
       <c r="AQ43" s="5">
-        <f>(SUM(AQ4:AQ42))*100</f>
         <v>3.4952499999999997E-2</v>
       </c>
     </row>
